--- a/api/templates/pk_xpert_workload_summary_report/en.xlsx
+++ b/api/templates/pk_xpert_workload_summary_report/en.xlsx
@@ -3,12 +3,11 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="1"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Deployment Wise" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="District Wise" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Definition" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Deployment Wise'!$A$7:$F$8</definedName>
@@ -103,7 +102,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t xml:space="preserve">Xpert Workload Summary Report</t>
   </si>
@@ -151,36 +150,6 @@
   </si>
   <si>
     <t>&lt;approvalStatus&gt;</t>
-  </si>
-  <si>
-    <t>Column</t>
-  </si>
-  <si>
-    <t>Data</t>
-  </si>
-  <si>
-    <t>Meaning</t>
-  </si>
-  <si>
-    <t>Blank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Use the last assay used</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GxAlert Active/Inactive</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Inactive if site is Inactive on GxAlert</t>
-  </si>
-  <si>
-    <t>Months</t>
-  </si>
-  <si>
-    <t>Month</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blanks are "0"</t>
   </si>
 </sst>
 </file>
@@ -1006,61 +975,4 @@
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
   <headerFooter/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
-  <cols>
-    <col customWidth="1" min="1" max="1" width="23.140625"/>
-    <col bestFit="1" customWidth="1" min="3" max="3" width="53.5703125"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-  </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
-  <headerFooter/>
-</worksheet>
 </file>
--- a/api/templates/pk_xpert_workload_summary_report/en.xlsx
+++ b/api/templates/pk_xpert_workload_summary_report/en.xlsx
@@ -1,113 +1,119 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26827"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-18.04\home\nsabaj\Repositories\aspect\api\templates\pk_xpert_workload_summary_report\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF7F0B41-03F9-48C6-881E-F48EC3788A26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Deployment Wise" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="District Wise" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Deployment Wise" sheetId="1" r:id="rId1"/>
+    <sheet name="District Wise" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Deployment Wise'!$A$7:$F$8</definedName>
     <definedName name="listbal" localSheetId="0">#REF!</definedName>
+    <definedName name="listbal" localSheetId="1">#REF!</definedName>
+    <definedName name="listbal">#REF!</definedName>
     <definedName name="listkpk" localSheetId="0">#REF!</definedName>
+    <definedName name="listkpk" localSheetId="1">#REF!</definedName>
+    <definedName name="listkpk">#REF!</definedName>
     <definedName name="listpunjab" localSheetId="0">#REF!</definedName>
+    <definedName name="listpunjab" localSheetId="1">#REF!</definedName>
+    <definedName name="listpunjab">#REF!</definedName>
     <definedName name="listsindh" localSheetId="0">#REF!</definedName>
+    <definedName name="listsindh" localSheetId="1">#REF!</definedName>
+    <definedName name="listsindh">#REF!</definedName>
     <definedName name="listtotal" localSheetId="0">#REF!</definedName>
+    <definedName name="listtotal" localSheetId="1">#REF!</definedName>
+    <definedName name="listtotal">#REF!</definedName>
     <definedName name="listultra" localSheetId="0">#REF!</definedName>
+    <definedName name="listultra" localSheetId="1">#REF!</definedName>
+    <definedName name="listultra">#REF!</definedName>
     <definedName name="listxpert" localSheetId="0">#REF!</definedName>
+    <definedName name="listxpert" localSheetId="1">#REF!</definedName>
+    <definedName name="listxpert">#REF!</definedName>
     <definedName name="ultraapr" localSheetId="0">#REF!</definedName>
+    <definedName name="ultraapr" localSheetId="1">#REF!</definedName>
+    <definedName name="ultraapr">#REF!</definedName>
     <definedName name="ultraapr1" localSheetId="0">#REF!</definedName>
+    <definedName name="ultraapr1" localSheetId="1">#REF!</definedName>
+    <definedName name="ultraapr1">#REF!</definedName>
     <definedName name="ultrafeb" localSheetId="0">#REF!</definedName>
+    <definedName name="ultrafeb" localSheetId="1">#REF!</definedName>
+    <definedName name="ultrafeb">#REF!</definedName>
     <definedName name="ultrafeb1" localSheetId="0">#REF!</definedName>
+    <definedName name="ultrafeb1" localSheetId="1">#REF!</definedName>
+    <definedName name="ultrafeb1">#REF!</definedName>
     <definedName name="ultrajan" localSheetId="0">#REF!</definedName>
+    <definedName name="ultrajan" localSheetId="1">#REF!</definedName>
+    <definedName name="ultrajan">#REF!</definedName>
     <definedName name="ULTRAJAN1" localSheetId="0">#REF!</definedName>
+    <definedName name="ULTRAJAN1" localSheetId="1">#REF!</definedName>
+    <definedName name="ULTRAJAN1">#REF!</definedName>
     <definedName name="ultrajul" localSheetId="0">#REF!</definedName>
+    <definedName name="ultrajul" localSheetId="1">#REF!</definedName>
+    <definedName name="ultrajul">#REF!</definedName>
     <definedName name="ultrajul1" localSheetId="0">#REF!</definedName>
+    <definedName name="ultrajul1" localSheetId="1">#REF!</definedName>
+    <definedName name="ultrajul1">#REF!</definedName>
     <definedName name="ultrajun" localSheetId="0">#REF!</definedName>
+    <definedName name="ultrajun" localSheetId="1">#REF!</definedName>
+    <definedName name="ultrajun">#REF!</definedName>
     <definedName name="ultrajun1" localSheetId="0">#REF!</definedName>
+    <definedName name="ultrajun1" localSheetId="1">#REF!</definedName>
+    <definedName name="ultrajun1">#REF!</definedName>
     <definedName name="ultramar" localSheetId="0">#REF!</definedName>
+    <definedName name="ultramar" localSheetId="1">#REF!</definedName>
+    <definedName name="ultramar">#REF!</definedName>
     <definedName name="ultramar1" localSheetId="0">#REF!</definedName>
+    <definedName name="ultramar1" localSheetId="1">#REF!</definedName>
+    <definedName name="ultramar1">#REF!</definedName>
     <definedName name="ultramay" localSheetId="0">#REF!</definedName>
+    <definedName name="ultramay" localSheetId="1">#REF!</definedName>
+    <definedName name="ultramay">#REF!</definedName>
     <definedName name="ultramay1" localSheetId="0">#REF!</definedName>
+    <definedName name="ultramay1" localSheetId="1">#REF!</definedName>
+    <definedName name="ultramay1">#REF!</definedName>
     <definedName name="xpertapr" localSheetId="0">#REF!</definedName>
+    <definedName name="xpertapr" localSheetId="1">#REF!</definedName>
+    <definedName name="xpertapr">#REF!</definedName>
     <definedName name="xpertfeb" localSheetId="0">#REF!</definedName>
+    <definedName name="xpertfeb" localSheetId="1">#REF!</definedName>
+    <definedName name="xpertfeb">#REF!</definedName>
     <definedName name="xpertjan" localSheetId="0">#REF!</definedName>
+    <definedName name="xpertjan" localSheetId="1">#REF!</definedName>
+    <definedName name="xpertjan">#REF!</definedName>
     <definedName name="xpertjul" localSheetId="0">#REF!</definedName>
+    <definedName name="xpertjul" localSheetId="1">#REF!</definedName>
+    <definedName name="xpertjul">#REF!</definedName>
     <definedName name="xpertjun" localSheetId="0">#REF!</definedName>
+    <definedName name="xpertjun" localSheetId="1">#REF!</definedName>
+    <definedName name="xpertjun">#REF!</definedName>
     <definedName name="xpertmar" localSheetId="0">#REF!</definedName>
+    <definedName name="xpertmar" localSheetId="1">#REF!</definedName>
+    <definedName name="xpertmar">#REF!</definedName>
     <definedName name="xpertmay" localSheetId="0">#REF!</definedName>
-    <definedName name="listbal" localSheetId="1">#REF!</definedName>
-    <definedName name="listkpk" localSheetId="1">#REF!</definedName>
-    <definedName name="listpunjab" localSheetId="1">#REF!</definedName>
-    <definedName name="listsindh" localSheetId="1">#REF!</definedName>
-    <definedName name="listtotal" localSheetId="1">#REF!</definedName>
-    <definedName name="listultra" localSheetId="1">#REF!</definedName>
-    <definedName name="listxpert" localSheetId="1">#REF!</definedName>
-    <definedName name="ultraapr" localSheetId="1">#REF!</definedName>
-    <definedName name="ultraapr1" localSheetId="1">#REF!</definedName>
-    <definedName name="ultrafeb" localSheetId="1">#REF!</definedName>
-    <definedName name="ultrafeb1" localSheetId="1">#REF!</definedName>
-    <definedName name="ultrajan" localSheetId="1">#REF!</definedName>
-    <definedName name="ULTRAJAN1" localSheetId="1">#REF!</definedName>
-    <definedName name="ultrajul" localSheetId="1">#REF!</definedName>
-    <definedName name="ultrajul1" localSheetId="1">#REF!</definedName>
-    <definedName name="ultrajun" localSheetId="1">#REF!</definedName>
-    <definedName name="ultrajun1" localSheetId="1">#REF!</definedName>
-    <definedName name="ultramar" localSheetId="1">#REF!</definedName>
-    <definedName name="ultramar1" localSheetId="1">#REF!</definedName>
-    <definedName name="ultramay" localSheetId="1">#REF!</definedName>
-    <definedName name="ultramay1" localSheetId="1">#REF!</definedName>
-    <definedName name="xpertapr" localSheetId="1">#REF!</definedName>
-    <definedName name="xpertfeb" localSheetId="1">#REF!</definedName>
-    <definedName name="xpertjan" localSheetId="1">#REF!</definedName>
-    <definedName name="xpertjul" localSheetId="1">#REF!</definedName>
-    <definedName name="xpertjun" localSheetId="1">#REF!</definedName>
-    <definedName name="xpertmar" localSheetId="1">#REF!</definedName>
     <definedName name="xpertmay" localSheetId="1">#REF!</definedName>
-    <definedName name="listbal">#REF!</definedName>
-    <definedName name="listkpk">#REF!</definedName>
-    <definedName name="listpunjab">#REF!</definedName>
-    <definedName name="listsindh">#REF!</definedName>
-    <definedName name="listtotal">#REF!</definedName>
-    <definedName name="listultra">#REF!</definedName>
-    <definedName name="listxpert">#REF!</definedName>
-    <definedName name="ultraapr">#REF!</definedName>
-    <definedName name="ultraapr1">#REF!</definedName>
-    <definedName name="ultrafeb">#REF!</definedName>
-    <definedName name="ultrafeb1">#REF!</definedName>
-    <definedName name="ultrajan">#REF!</definedName>
-    <definedName name="ULTRAJAN1">#REF!</definedName>
-    <definedName name="ultrajul">#REF!</definedName>
-    <definedName name="ultrajul1">#REF!</definedName>
-    <definedName name="ultrajun">#REF!</definedName>
-    <definedName name="ultrajun1">#REF!</definedName>
-    <definedName name="ultramar">#REF!</definedName>
-    <definedName name="ultramar1">#REF!</definedName>
-    <definedName name="ultramay">#REF!</definedName>
-    <definedName name="ultramay1">#REF!</definedName>
-    <definedName name="xpertapr">#REF!</definedName>
-    <definedName name="xpertfeb">#REF!</definedName>
-    <definedName name="xpertjan">#REF!</definedName>
-    <definedName name="xpertjul">#REF!</definedName>
-    <definedName name="xpertjun">#REF!</definedName>
-    <definedName name="xpertmar">#REF!</definedName>
     <definedName name="xpertmay">#REF!</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Deployment Wise'!$A$7:$F$8</definedName>
   </definedNames>
-  <calcPr calcOnSave="0" concurrentCalc="0"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
-  <si>
-    <t xml:space="preserve">Xpert Workload Summary Report</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dates: &lt;Dates&gt;</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="16">
+  <si>
+    <t>Xpert Workload Summary Report</t>
+  </si>
+  <si>
+    <t>Dates: &lt;Dates&gt;</t>
   </si>
   <si>
     <t>&lt;Table&gt;</t>
@@ -122,15 +128,12 @@
     <t xml:space="preserve">Name GeneXpert deployments </t>
   </si>
   <si>
-    <t xml:space="preserve">Assay Used</t>
+    <t>Assay Used</t>
   </si>
   <si>
     <t>Responsible</t>
   </si>
   <si>
-    <t xml:space="preserve">Aspect Approval Status</t>
-  </si>
-  <si>
     <t xml:space="preserve">MTB RIF/Ultra </t>
   </si>
   <si>
@@ -149,50 +152,53 @@
     <t>&lt;responsible&gt;</t>
   </si>
   <si>
-    <t>&lt;approvalStatus&gt;</t>
+    <t>Device Maintenance Status</t>
+  </si>
+  <si>
+    <t>&lt;maintenanceStatus&gt;</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="7">
     <font>
-      <sz val="11.000000"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="16.000000"/>
+      <sz val="16"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="11.000000"/>
+      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="11.000000"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11.000000"/>
+      <sz val="11"/>
       <color indexed="2"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11.000000"/>
+      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="11.000000"/>
+      <sz val="11"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
@@ -262,39 +268,42 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
-    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf fontId="2" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf fontId="3" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+  <cellXfs count="15">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="3" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="3" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="3" fillId="2" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="3" fillId="2" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="3" fillId="2" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf fontId="3" fillId="2" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="4" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf fontId="5" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="6" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf fontId="5" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -305,295 +314,15 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
-  <a:themeElements>
-    <a:clrScheme name="Office">
-      <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
-      </a:dk1>
-      <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
-      </a:lt1>
-      <a:dk2>
-        <a:srgbClr val="1F497D"/>
-      </a:dk2>
-      <a:lt2>
-        <a:srgbClr val="EEECE1"/>
-      </a:lt2>
-      <a:accent1>
-        <a:srgbClr val="4F81BD"/>
-      </a:accent1>
-      <a:accent2>
-        <a:srgbClr val="C0504D"/>
-      </a:accent2>
-      <a:accent3>
-        <a:srgbClr val="9BBB59"/>
-      </a:accent3>
-      <a:accent4>
-        <a:srgbClr val="8064A2"/>
-      </a:accent4>
-      <a:accent5>
-        <a:srgbClr val="4BACC6"/>
-      </a:accent5>
-      <a:accent6>
-        <a:srgbClr val="F79646"/>
-      </a:accent6>
-      <a:hlink>
-        <a:srgbClr val="0000FF"/>
-      </a:hlink>
-      <a:folHlink>
-        <a:srgbClr val="800080"/>
-      </a:folHlink>
-    </a:clrScheme>
-    <a:fontScheme name="Office">
-      <a:majorFont>
-        <a:latin typeface="Cambria"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Angsana New"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ 明朝"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Cordia New"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-      </a:minorFont>
-    </a:fontScheme>
-    <a:fmtScheme name="Office">
-      <a:fillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="35000">
-              <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
-        </a:gradFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
-        </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="40000">
-              <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
-        </a:gradFill>
-      </a:bgFillStyleLst>
-    </a:fmtScheme>
-  </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-</a:theme>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -798,32 +527,34 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="18" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="24.140625"/>
-    <col customWidth="1" min="2" max="2" width="27.42578125"/>
-    <col customWidth="1" min="3" max="3" width="23.5703125"/>
-    <col customWidth="1" min="4" max="4" width="26"/>
-    <col customWidth="1" min="5" max="5" width="17.140625"/>
-    <col customWidth="1" min="6" max="6" width="17.42578125"/>
+    <col min="1" max="1" width="24.109375" customWidth="1"/>
+    <col min="2" max="2" width="27.44140625" customWidth="1"/>
+    <col min="3" max="3" width="23.5546875" customWidth="1"/>
+    <col min="4" max="4" width="26" customWidth="1"/>
+    <col min="5" max="5" width="17.109375" customWidth="1"/>
+    <col min="6" max="6" width="17.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1">
+    <row r="1" spans="1:6" ht="18" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" ht="18" customHeight="1">
+    <row r="2" spans="1:6" ht="18" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="5" ht="18" customHeight="1">
+    <row r="5" spans="1:6" ht="18" customHeight="1">
       <c r="A5" t="s">
         <v>2</v>
       </c>
@@ -831,58 +562,58 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" s="3" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A6" s="4" t="s">
+    <row r="6" spans="1:6" s="3" customFormat="1" ht="22.5" customHeight="1">
+      <c r="A6" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="10" t="s">
         <v>5</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E6" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F6" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="14.4">
+      <c r="A7" s="9"/>
+      <c r="B7" s="9"/>
+      <c r="C7" s="10"/>
+      <c r="D7" s="4" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="7" ht="28.5">
-      <c r="A7" s="4"/>
-      <c r="B7" s="4"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="4" t="s">
+      <c r="E7" s="12"/>
+      <c r="F7" s="14"/>
+    </row>
+    <row r="8" spans="1:6" s="5" customFormat="1" ht="18" customHeight="1">
+      <c r="A8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="E7" s="8"/>
-      <c r="F7" s="9"/>
-    </row>
-    <row r="8" s="10" customFormat="1" ht="18" customHeight="1">
-      <c r="A8" s="11" t="s">
+      <c r="B8" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="C8" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="13" t="s">
+      <c r="D8" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="D8" s="13" t="s">
+      <c r="E8" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="E8" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="F8" s="13" t="s">
+      <c r="F8" s="8" t="s">
         <v>15</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A7:F8"/>
+  <autoFilter ref="A7:F8" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="5">
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="B6:B7"/>
@@ -890,37 +621,36 @@
     <mergeCell ref="E6:E7"/>
     <mergeCell ref="F6:F7"/>
   </mergeCells>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700776" bottom="0.75196850393700776" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700776" bottom="0.75196850393700776" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:D8"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="18" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="25.42578125"/>
-    <col customWidth="1" min="2" max="2" width="18.28515625"/>
-    <col customWidth="1" min="3" max="3" width="26.42578125"/>
-    <col bestFit="1" customWidth="1" min="4" max="4" width="15.7109375"/>
+    <col min="1" max="1" width="25.44140625" customWidth="1"/>
+    <col min="2" max="2" width="18.33203125" customWidth="1"/>
+    <col min="3" max="3" width="26.44140625" customWidth="1"/>
+    <col min="4" max="4" width="17.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1">
+    <row r="1" spans="1:4" ht="18" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" ht="18" customHeight="1">
+    <row r="2" spans="1:4" ht="18" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" ht="18" customHeight="1">
+    <row r="3" spans="1:4" ht="18" customHeight="1">
       <c r="A3" s="2"/>
     </row>
-    <row r="5" ht="18" customHeight="1">
+    <row r="5" spans="1:4" ht="18" customHeight="1">
       <c r="A5" t="s">
         <v>2</v>
       </c>
@@ -928,40 +658,40 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="4" t="s">
+    <row r="6" spans="1:4" ht="18" customHeight="1">
+      <c r="A6" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="9" t="s">
         <v>4</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="11" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="4"/>
-      <c r="B7" s="4"/>
+    <row r="7" spans="1:4" ht="18" customHeight="1">
+      <c r="A7" s="9"/>
+      <c r="B7" s="9"/>
       <c r="C7" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="12"/>
+    </row>
+    <row r="8" spans="1:4" ht="18" customHeight="1">
+      <c r="A8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="8"/>
-    </row>
-    <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="11" t="s">
+      <c r="B8" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" s="13" t="s">
+      <c r="C8" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" s="8" t="s">
         <v>13</v>
-      </c>
-      <c r="D8" s="13" t="s">
-        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -970,9 +700,7 @@
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="D6:D7"/>
   </mergeCells>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="portrait"/>
 </worksheet>
 </file>
--- a/api/templates/pk_xpert_workload_summary_report/en.xlsx
+++ b/api/templates/pk_xpert_workload_summary_report/en.xlsx
@@ -1,114 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26827"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-18.04\home\nsabaj\Repositories\aspect\api\templates\pk_xpert_workload_summary_report\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF7F0B41-03F9-48C6-881E-F48EC3788A26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456"/>
   </bookViews>
   <sheets>
-    <sheet name="Deployment Wise" sheetId="1" r:id="rId1"/>
-    <sheet name="District Wise" sheetId="2" r:id="rId2"/>
+    <sheet sheetId="1" name="Deployment Wise" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="District Wise" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Deployment Wise'!$A$7:$F$8</definedName>
-    <definedName name="listbal" localSheetId="0">#REF!</definedName>
-    <definedName name="listbal" localSheetId="1">#REF!</definedName>
-    <definedName name="listbal">#REF!</definedName>
-    <definedName name="listkpk" localSheetId="0">#REF!</definedName>
-    <definedName name="listkpk" localSheetId="1">#REF!</definedName>
-    <definedName name="listkpk">#REF!</definedName>
-    <definedName name="listpunjab" localSheetId="0">#REF!</definedName>
-    <definedName name="listpunjab" localSheetId="1">#REF!</definedName>
-    <definedName name="listpunjab">#REF!</definedName>
-    <definedName name="listsindh" localSheetId="0">#REF!</definedName>
-    <definedName name="listsindh" localSheetId="1">#REF!</definedName>
-    <definedName name="listsindh">#REF!</definedName>
-    <definedName name="listtotal" localSheetId="0">#REF!</definedName>
-    <definedName name="listtotal" localSheetId="1">#REF!</definedName>
-    <definedName name="listtotal">#REF!</definedName>
-    <definedName name="listultra" localSheetId="0">#REF!</definedName>
-    <definedName name="listultra" localSheetId="1">#REF!</definedName>
-    <definedName name="listultra">#REF!</definedName>
-    <definedName name="listxpert" localSheetId="0">#REF!</definedName>
-    <definedName name="listxpert" localSheetId="1">#REF!</definedName>
-    <definedName name="listxpert">#REF!</definedName>
-    <definedName name="ultraapr" localSheetId="0">#REF!</definedName>
-    <definedName name="ultraapr" localSheetId="1">#REF!</definedName>
-    <definedName name="ultraapr">#REF!</definedName>
-    <definedName name="ultraapr1" localSheetId="0">#REF!</definedName>
-    <definedName name="ultraapr1" localSheetId="1">#REF!</definedName>
-    <definedName name="ultraapr1">#REF!</definedName>
-    <definedName name="ultrafeb" localSheetId="0">#REF!</definedName>
-    <definedName name="ultrafeb" localSheetId="1">#REF!</definedName>
-    <definedName name="ultrafeb">#REF!</definedName>
-    <definedName name="ultrafeb1" localSheetId="0">#REF!</definedName>
-    <definedName name="ultrafeb1" localSheetId="1">#REF!</definedName>
-    <definedName name="ultrafeb1">#REF!</definedName>
-    <definedName name="ultrajan" localSheetId="0">#REF!</definedName>
-    <definedName name="ultrajan" localSheetId="1">#REF!</definedName>
-    <definedName name="ultrajan">#REF!</definedName>
-    <definedName name="ULTRAJAN1" localSheetId="0">#REF!</definedName>
-    <definedName name="ULTRAJAN1" localSheetId="1">#REF!</definedName>
-    <definedName name="ULTRAJAN1">#REF!</definedName>
-    <definedName name="ultrajul" localSheetId="0">#REF!</definedName>
-    <definedName name="ultrajul" localSheetId="1">#REF!</definedName>
-    <definedName name="ultrajul">#REF!</definedName>
-    <definedName name="ultrajul1" localSheetId="0">#REF!</definedName>
-    <definedName name="ultrajul1" localSheetId="1">#REF!</definedName>
-    <definedName name="ultrajul1">#REF!</definedName>
-    <definedName name="ultrajun" localSheetId="0">#REF!</definedName>
-    <definedName name="ultrajun" localSheetId="1">#REF!</definedName>
-    <definedName name="ultrajun">#REF!</definedName>
-    <definedName name="ultrajun1" localSheetId="0">#REF!</definedName>
-    <definedName name="ultrajun1" localSheetId="1">#REF!</definedName>
-    <definedName name="ultrajun1">#REF!</definedName>
-    <definedName name="ultramar" localSheetId="0">#REF!</definedName>
-    <definedName name="ultramar" localSheetId="1">#REF!</definedName>
-    <definedName name="ultramar">#REF!</definedName>
-    <definedName name="ultramar1" localSheetId="0">#REF!</definedName>
-    <definedName name="ultramar1" localSheetId="1">#REF!</definedName>
-    <definedName name="ultramar1">#REF!</definedName>
-    <definedName name="ultramay" localSheetId="0">#REF!</definedName>
-    <definedName name="ultramay" localSheetId="1">#REF!</definedName>
-    <definedName name="ultramay">#REF!</definedName>
-    <definedName name="ultramay1" localSheetId="0">#REF!</definedName>
-    <definedName name="ultramay1" localSheetId="1">#REF!</definedName>
-    <definedName name="ultramay1">#REF!</definedName>
-    <definedName name="xpertapr" localSheetId="0">#REF!</definedName>
-    <definedName name="xpertapr" localSheetId="1">#REF!</definedName>
-    <definedName name="xpertapr">#REF!</definedName>
-    <definedName name="xpertfeb" localSheetId="0">#REF!</definedName>
-    <definedName name="xpertfeb" localSheetId="1">#REF!</definedName>
-    <definedName name="xpertfeb">#REF!</definedName>
-    <definedName name="xpertjan" localSheetId="0">#REF!</definedName>
-    <definedName name="xpertjan" localSheetId="1">#REF!</definedName>
-    <definedName name="xpertjan">#REF!</definedName>
-    <definedName name="xpertjul" localSheetId="0">#REF!</definedName>
-    <definedName name="xpertjul" localSheetId="1">#REF!</definedName>
-    <definedName name="xpertjul">#REF!</definedName>
-    <definedName name="xpertjun" localSheetId="0">#REF!</definedName>
-    <definedName name="xpertjun" localSheetId="1">#REF!</definedName>
-    <definedName name="xpertjun">#REF!</definedName>
-    <definedName name="xpertmar" localSheetId="0">#REF!</definedName>
-    <definedName name="xpertmar" localSheetId="1">#REF!</definedName>
-    <definedName name="xpertmar">#REF!</definedName>
-    <definedName name="xpertmay" localSheetId="0">#REF!</definedName>
-    <definedName name="xpertmay" localSheetId="1">#REF!</definedName>
-    <definedName name="xpertmay">#REF!</definedName>
+    <definedName name="_xlnm._FilterDatabase">'Deployment Wise'!$A$7:$F$8</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="17">
   <si>
     <t>Xpert Workload Summary Report</t>
   </si>
@@ -116,6 +26,9 @@
     <t>Dates: &lt;Dates&gt;</t>
   </si>
   <si>
+    <t>&lt;DecommissionedDevicesLabel&gt;: &lt;DecommissionedDevices&gt;</t>
+  </si>
+  <si>
     <t>&lt;Table&gt;</t>
   </si>
   <si>
@@ -134,6 +47,9 @@
     <t>Responsible</t>
   </si>
   <si>
+    <t>Device Maintenance Status</t>
+  </si>
+  <si>
     <t xml:space="preserve">MTB RIF/Ultra </t>
   </si>
   <si>
@@ -150,9 +66,6 @@
   </si>
   <si>
     <t>&lt;responsible&gt;</t>
-  </si>
-  <si>
-    <t>Device Maintenance Status</t>
   </si>
   <si>
     <t>&lt;maintenanceStatus&gt;</t>
@@ -161,13 +74,14 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
+      <color theme="1"/>
+      <family val="2"/>
+      <scheme val="minor"/>
       <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -180,17 +94,17 @@
     </font>
     <font>
       <b/>
+      <color theme="1"/>
+      <scheme val="minor"/>
       <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
+      <color indexed="2"/>
+      <scheme val="minor"/>
       <sz val="11"/>
-      <color indexed="2"/>
       <name val="Calibri"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -198,9 +112,9 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <scheme val="minor"/>
       <sz val="11"/>
       <name val="Calibri"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -212,8 +126,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79995117038483843"/>
-        <bgColor theme="4" tint="0.79995117038483843"/>
+        <fgColor theme="4" tint="0.7999511703848384"/>
+        <bgColor theme="4" tint="0.7999511703848384"/>
       </patternFill>
     </fill>
   </fills>
@@ -226,51 +140,31 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
+      <left style="thin"/>
+      <right style="thin"/>
       <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -280,30 +174,27 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -532,9 +423,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F8"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="18" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="18" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="9.109375" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="24.109375" customWidth="1"/>
     <col min="2" max="2" width="27.44140625" customWidth="1"/>
@@ -544,76 +435,81 @@
     <col min="6" max="6" width="17.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="18" customHeight="1">
+    <row r="1" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="18" customHeight="1">
+    <row r="2" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="18" customHeight="1">
+    <row r="3" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B5">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:6" s="3" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A6" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="9" t="s">
+    <row r="6" ht="22.5" customHeight="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="B6" s="4" t="s">
         <v>5</v>
       </c>
+      <c r="C6" s="5" t="s">
+        <v>6</v>
+      </c>
       <c r="D6" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="E6" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="F6" s="13" t="s">
+      <c r="E6" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" ht="14.4" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="4"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" s="8"/>
+      <c r="F7" s="9"/>
+    </row>
+    <row r="8" ht="18" customHeight="1" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" s="13" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" ht="14.4">
-      <c r="A7" s="9"/>
-      <c r="B7" s="9"/>
-      <c r="C7" s="10"/>
-      <c r="D7" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E7" s="12"/>
-      <c r="F7" s="14"/>
-    </row>
-    <row r="8" spans="1:6" s="5" customFormat="1" ht="18" customHeight="1">
-      <c r="A8" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F8" s="8" t="s">
+      <c r="E8" s="13" t="s">
         <v>15</v>
       </c>
+      <c r="F8" s="13" t="s">
+        <v>16</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A7:F8" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A7:F8"/>
   <mergeCells count="5">
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="B6:B7"/>
@@ -621,15 +517,15 @@
     <mergeCell ref="E6:E7"/>
     <mergeCell ref="F6:F7"/>
   </mergeCells>
-  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700776" bottom="0.75196850393700776" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape"/>
+  <pageMargins left="0.7007874015748032" right="0.7007874015748032" top="0.7519685039370078" bottom="0.7519685039370078" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D8"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="18" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="18" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="9.109375" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="25.44140625" customWidth="1"/>
     <col min="2" max="2" width="18.33203125" customWidth="1"/>
@@ -637,61 +533,63 @@
     <col min="4" max="4" width="17.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="18" customHeight="1">
+    <row r="1" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="18" customHeight="1">
+    <row r="2" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="18" customHeight="1">
-      <c r="A3" s="2"/>
-    </row>
-    <row r="5" spans="1:4" ht="18" customHeight="1">
+    <row r="3" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B5">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="18" customHeight="1">
-      <c r="A6" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="9" t="s">
+    <row r="6" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
         <v>4</v>
       </c>
+      <c r="B6" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="C6" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D6" s="11" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" ht="18" customHeight="1">
-      <c r="A7" s="9"/>
-      <c r="B7" s="9"/>
+      <c r="D6" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="4"/>
+      <c r="B7" s="4"/>
       <c r="C7" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D7" s="12"/>
-    </row>
-    <row r="8" spans="1:4" ht="18" customHeight="1">
-      <c r="A8" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="D7" s="8"/>
+    </row>
+    <row r="8" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="D8" s="8" t="s">
-        <v>13</v>
+      <c r="C8" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -701,6 +599,6 @@
     <mergeCell ref="D6:D7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" fitToHeight="0" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/api/templates/pk_xpert_workload_summary_report/en.xlsx
+++ b/api/templates/pk_xpert_workload_summary_report/en.xlsx
@@ -167,7 +167,7 @@
   <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>

--- a/api/templates/pk_xpert_workload_summary_report/en.xlsx
+++ b/api/templates/pk_xpert_workload_summary_report/en.xlsx
@@ -26,7 +26,7 @@
     <t>Dates: &lt;Dates&gt;</t>
   </si>
   <si>
-    <t>&lt;DecommissionedDevicesLabel&gt;: &lt;DecommissionedDevices&gt;</t>
+    <t>Decommissioned Devices: &lt;DecommissionedDevices&gt;</t>
   </si>
   <si>
     <t>&lt;Table&gt;</t>
@@ -167,7 +167,7 @@
   <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
